--- a/data/trans_camb/P26-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P26-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 13,43</t>
+          <t>0,5; 12,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 3,26</t>
+          <t>-8,54; 2,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,71; -7,63</t>
+          <t>-17,66; -8,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 12,55</t>
+          <t>-4,12; 12,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,36; 2,36</t>
+          <t>-12,14; 2,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,3; -11,44</t>
+          <t>-23,14; -11,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 10,92</t>
+          <t>1,22; 10,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 1,64</t>
+          <t>-7,58; 1,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-17,78; -10,35</t>
+          <t>-18,01; -10,85</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,7; 69,9</t>
+          <t>1,93; 66,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,19; 17,13</t>
+          <t>-35,01; 13,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-72,0; -40,18</t>
+          <t>-71,1; -40,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 53,61</t>
+          <t>-13,4; 52,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,63; 9,02</t>
+          <t>-37,64; 9,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-73,6; -48,17</t>
+          <t>-73,93; -50,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 50,24</t>
+          <t>5,0; 49,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,92; 7,49</t>
+          <t>-29,66; 6,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-68,87; -48,55</t>
+          <t>-69,17; -49,77</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 10,29</t>
+          <t>-3,11; 10,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 3,96</t>
+          <t>-9,2; 3,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,4; -7,54</t>
+          <t>-20,08; -7,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 3,98</t>
+          <t>-10,91; 3,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,45; -5,65</t>
+          <t>-19,59; -6,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,48; -17,13</t>
+          <t>-29,58; -17,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 4,64</t>
+          <t>-5,27; 4,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,93; -3,38</t>
+          <t>-12,42; -3,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-23,23; -14,28</t>
+          <t>-23,37; -14,55</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 52,02</t>
+          <t>-11,45; 57,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-34,68; 20,94</t>
+          <t>-35,06; 18,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-74,38; -38,31</t>
+          <t>-74,91; -33,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-28,08; 11,51</t>
+          <t>-27,7; 10,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,07; -18,16</t>
+          <t>-49,48; -18,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-74,42; -52,55</t>
+          <t>-73,84; -53,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,54; 16,94</t>
+          <t>-16,47; 17,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,87; -11,52</t>
+          <t>-38,34; -11,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-71,55; -51,8</t>
+          <t>-72,31; -53,55</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 10,79</t>
+          <t>0,11; 11,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 2,82</t>
+          <t>-7,85; 3,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,08; 53,18</t>
+          <t>-21,29; 52,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 9,88</t>
+          <t>-9,9; 9,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-33,19; -12,19</t>
+          <t>-32,89; -11,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-44,7; -26,77</t>
+          <t>-44,49; -27,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 9,82</t>
+          <t>0,18; 10,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,22; -2,05</t>
+          <t>-12,43; -2,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-24,69; 41,27</t>
+          <t>-24,84; 43,08</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,23; 42,5</t>
+          <t>0,16; 43,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-26,05; 10,8</t>
+          <t>-25,78; 14,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-73,45; 200,34</t>
+          <t>-73,77; 205,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,26; 25,9</t>
+          <t>-20,39; 25,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-67,26; -31,08</t>
+          <t>-66,02; -27,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-87,79; -68,21</t>
+          <t>-88,25; -68,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,03; 33,65</t>
+          <t>0,55; 34,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-35,58; -7,07</t>
+          <t>-35,76; -6,77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-75,85; 136,96</t>
+          <t>-75,91; 142,02</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 9,69</t>
+          <t>1,16; 9,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 2,99</t>
+          <t>-5,02; 2,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,19; -10,68</t>
+          <t>-18,61; -11,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 5,86</t>
+          <t>-5,35; 5,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-17,56; -7,1</t>
+          <t>-16,85; -6,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-36,48; -21,62</t>
+          <t>-36,65; -21,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 7,11</t>
+          <t>0,51; 6,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,81; -1,56</t>
+          <t>-8,06; -1,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-23,97; -15,51</t>
+          <t>-24,43; -15,89</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,09; 37,04</t>
+          <t>4,14; 36,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 11,48</t>
+          <t>-16,75; 11,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-61,54; -39,73</t>
+          <t>-62,2; -40,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 14,87</t>
+          <t>-12,25; 15,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-38,86; -17,8</t>
+          <t>-37,08; -16,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-82,68; -53,49</t>
+          <t>-83,79; -53,51</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,58; 22,84</t>
+          <t>1,42; 22,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-22,59; -5,1</t>
+          <t>-22,93; -5,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-71,35; -49,28</t>
+          <t>-72,36; -49,94</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 7,53</t>
+          <t>-6,06; 7,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,33; -2,17</t>
+          <t>-14,85; -1,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-24,96; -12,41</t>
+          <t>-25,31; -11,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 2,99</t>
+          <t>-9,25; 2,49</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-19,93; -8,57</t>
+          <t>-19,22; -8,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-35,98; -25,46</t>
+          <t>-37,41; -25,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 2,72</t>
+          <t>-6,65; 2,34</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-16,34; -7,73</t>
+          <t>-16,55; -7,97</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-30,25; -21,58</t>
+          <t>-30,25; -21,61</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 26,17</t>
+          <t>-16,94; 27,21</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-41,06; -7,65</t>
+          <t>-40,16; -5,36</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-68,67; -42,4</t>
+          <t>-69,56; -40,91</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-18,4; 7,29</t>
+          <t>-19,21; 6,16</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-41,8; -20,56</t>
+          <t>-40,53; -19,95</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-77,61; -61,68</t>
+          <t>-78,32; -61,74</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 7,29</t>
+          <t>-15,87; 6,25</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-38,27; -20,69</t>
+          <t>-39,13; -21,42</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-72,59; -57,9</t>
+          <t>-72,33; -57,95</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 5,83</t>
+          <t>-11,11; 4,88</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-18,29; -2,32</t>
+          <t>-18,18; -1,89</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-39,81; -19,25</t>
+          <t>-38,65; -19,42</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,31; 9,51</t>
+          <t>1,41; 9,35</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-11,63; -3,6</t>
+          <t>-11,53; -3,42</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-24,23; -16,26</t>
+          <t>-24,0; -15,57</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 6,97</t>
+          <t>-0,38; 6,99</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-11,81; -4,93</t>
+          <t>-12,01; -4,78</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-25,71; -18,02</t>
+          <t>-25,88; -18,18</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-21,61; 14,8</t>
+          <t>-21,73; 11,95</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-37,32; -5,38</t>
+          <t>-37,98; -4,68</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-82,84; -44,83</t>
+          <t>-81,08; -43,78</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4,12; 30,91</t>
+          <t>4,26; 30,82</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-34,25; -11,79</t>
+          <t>-34,17; -11,08</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-70,54; -50,38</t>
+          <t>-70,6; -50,74</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 21,05</t>
+          <t>-0,92; 20,97</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-32,46; -14,81</t>
+          <t>-32,21; -14,21</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-70,28; -52,83</t>
+          <t>-70,8; -53,05</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,43</t>
+          <t>1,94; 6,5</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,68; -1,13</t>
+          <t>-5,65; -1,14</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-17,75; 13,79</t>
+          <t>-17,54; 12,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 3,93</t>
+          <t>-0,85; 4,21</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-12,63; -7,95</t>
+          <t>-12,95; -8,1</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-27,17; -21,98</t>
+          <t>-27,14; -22,02</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,64</t>
+          <t>1,24; 4,74</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-8,65; -5,38</t>
+          <t>-8,71; -5,36</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-21,19; -6,69</t>
+          <t>-21,19; -4,77</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>6,43; 23,73</t>
+          <t>6,46; 23,46</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-19,19; -4,25</t>
+          <t>-18,96; -3,92</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-61,37; 49,02</t>
+          <t>-61,04; 43,13</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 11,11</t>
+          <t>-2,22; 11,71</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-33,4; -22,24</t>
+          <t>-33,75; -22,77</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-72,39; -60,96</t>
+          <t>-72,02; -61,21</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,04; 14,54</t>
+          <t>3,74; 14,72</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-25,6; -16,81</t>
+          <t>-25,74; -16,65</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-63,97; -20,85</t>
+          <t>-64,33; -15,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P26-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P26-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-12,7</t>
+          <t>-12,61</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-17,45</t>
+          <t>-17,37</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-14,44</t>
+          <t>-14,36</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 12,66</t>
+          <t>1,29; 13,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 2,56</t>
+          <t>-8,48; 2,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,66; -8,07</t>
+          <t>-17,25; -7,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 12,83</t>
+          <t>-3,09; 11,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 2,2</t>
+          <t>-11,17; 2,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,14; -11,86</t>
+          <t>-23,55; -11,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 10,69</t>
+          <t>1,58; 11,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 1,73</t>
+          <t>-7,41; 1,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-18,01; -10,85</t>
+          <t>-18,09; -10,56</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-58,43%</t>
+          <t>-58,04%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-63,5%</t>
+          <t>-63,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-60,32%</t>
+          <t>-59,97%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,93; 66,99</t>
+          <t>5,19; 75,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-35,01; 13,45</t>
+          <t>-34,94; 14,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-71,1; -40,52</t>
+          <t>-70,43; -40,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 52,97</t>
+          <t>-10,28; 50,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,64; 9,71</t>
+          <t>-35,57; 12,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-73,93; -50,03</t>
+          <t>-73,81; -49,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,0; 49,74</t>
+          <t>5,79; 52,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,66; 6,99</t>
+          <t>-28,72; 6,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-69,17; -49,77</t>
+          <t>-68,26; -49,48</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-13,83</t>
+          <t>-14,82</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-18,99</t>
+          <t>-19,48</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 10,99</t>
+          <t>-2,45; 10,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 3,37</t>
+          <t>-9,1; 4,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,08; -7,44</t>
+          <t>-20,42; -9,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 3,41</t>
+          <t>-11,29; 4,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,59; -6,08</t>
+          <t>-19,77; -6,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,58; -17,89</t>
+          <t>-29,56; -17,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 4,62</t>
+          <t>-5,56; 4,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,42; -3,22</t>
+          <t>-12,17; -3,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-23,37; -14,55</t>
+          <t>-23,64; -15,31</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-60,54%</t>
+          <t>-64,86%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-63,89%</t>
+          <t>-65,54%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 57,15</t>
+          <t>-9,33; 56,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-35,06; 18,17</t>
+          <t>-34,18; 22,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-74,91; -33,91</t>
+          <t>-76,9; -46,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,7; 10,2</t>
+          <t>-29,06; 12,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,48; -18,02</t>
+          <t>-50,29; -18,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,84; -53,98</t>
+          <t>-73,51; -53,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,47; 17,03</t>
+          <t>-17,2; 15,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,34; -11,34</t>
+          <t>-38,56; -11,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-72,31; -53,55</t>
+          <t>-73,14; -55,66</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15,77</t>
+          <t>-19,44</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-35,19</t>
+          <t>-35,29</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,39</t>
+          <t>-23,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 11,03</t>
+          <t>0,22; 11,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 3,55</t>
+          <t>-8,16; 3,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,29; 52,59</t>
+          <t>-24,07; -14,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 9,42</t>
+          <t>-10,5; 10,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-32,89; -11,8</t>
+          <t>-32,96; -10,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-44,49; -27,01</t>
+          <t>-43,84; -26,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 10,13</t>
+          <t>-0,4; 9,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,43; -2,02</t>
+          <t>-12,18; -2,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-24,84; 43,08</t>
+          <t>-27,82; -19,0</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>-68,94%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-80,32%</t>
+          <t>-80,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>-72,68%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,16; 43,82</t>
+          <t>0,86; 44,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-25,78; 14,33</t>
+          <t>-26,67; 13,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-73,77; 205,13</t>
+          <t>-78,19; -55,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,39; 25,13</t>
+          <t>-21,88; 28,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-66,02; -27,45</t>
+          <t>-67,43; -28,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-88,25; -68,03</t>
+          <t>-88,15; -69,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 34,45</t>
+          <t>-1,21; 32,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-35,76; -6,77</t>
+          <t>-36,11; -7,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-75,91; 142,02</t>
+          <t>-79,83; -63,86</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-14,53</t>
+          <t>-14,78</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-27,54</t>
+          <t>-24,09</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-19,19</t>
+          <t>-17,85</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 9,35</t>
+          <t>1,53; 9,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 2,96</t>
+          <t>-4,88; 3,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,61; -11,14</t>
+          <t>-18,41; -11,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 5,93</t>
+          <t>-5,55; 5,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-16,85; -6,77</t>
+          <t>-17,18; -6,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-36,65; -21,51</t>
+          <t>-28,61; -19,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 6,96</t>
+          <t>0,52; 7,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,06; -1,59</t>
+          <t>-7,84; -1,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-24,43; -15,89</t>
+          <t>-20,85; -14,71</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-52,09%</t>
+          <t>-52,98%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-65,96%</t>
+          <t>-57,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-58,19%</t>
+          <t>-54,15%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,14; 36,83</t>
+          <t>5,17; 38,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 11,47</t>
+          <t>-16,13; 11,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-62,2; -40,68</t>
+          <t>-62,42; -42,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 15,45</t>
+          <t>-12,36; 13,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,08; -16,74</t>
+          <t>-37,94; -15,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-83,79; -53,51</t>
+          <t>-63,78; -49,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,42; 22,4</t>
+          <t>1,42; 22,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-22,93; -5,16</t>
+          <t>-22,72; -5,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-72,36; -49,94</t>
+          <t>-60,21; -46,38</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-18,41</t>
+          <t>-18,17</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-30,44</t>
+          <t>-28,94</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-25,87</t>
+          <t>-24,87</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 7,58</t>
+          <t>-6,93; 6,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,85; -1,69</t>
+          <t>-14,48; -2,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-25,31; -11,83</t>
+          <t>-24,7; -11,64</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 2,49</t>
+          <t>-9,21; 2,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-19,22; -8,17</t>
+          <t>-19,87; -8,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-37,41; -25,67</t>
+          <t>-33,89; -23,65</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 2,34</t>
+          <t>-6,4; 2,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-16,55; -7,97</t>
+          <t>-16,46; -8,09</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-30,25; -21,61</t>
+          <t>-28,61; -20,9</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-57,03%</t>
+          <t>-56,28%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-68,83%</t>
+          <t>-65,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-65,19%</t>
+          <t>-62,65%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-16,94; 27,21</t>
+          <t>-18,34; 24,02</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-40,16; -5,36</t>
+          <t>-40,02; -7,29</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-69,56; -40,91</t>
+          <t>-67,28; -40,38</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-19,21; 6,16</t>
+          <t>-18,99; 6,69</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-40,53; -19,95</t>
+          <t>-41,52; -20,11</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-78,32; -61,74</t>
+          <t>-70,87; -58,42</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 6,25</t>
+          <t>-15,32; 6,86</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-39,13; -21,42</t>
+          <t>-38,66; -21,43</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-72,33; -57,95</t>
+          <t>-67,77; -56,25</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-29,91</t>
+          <t>-30,83</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-20,28</t>
+          <t>-21,16</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-22,13</t>
+          <t>-23,07</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 4,88</t>
+          <t>-11,43; 5,95</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-18,18; -1,89</t>
+          <t>-19,07; -2,29</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-38,65; -19,42</t>
+          <t>-39,0; -20,77</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,41; 9,35</t>
+          <t>0,72; 9,6</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-11,53; -3,42</t>
+          <t>-11,87; -4,31</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-24,0; -15,57</t>
+          <t>-24,98; -17,33</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 6,99</t>
+          <t>-0,35; 6,94</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-12,01; -4,78</t>
+          <t>-11,61; -4,47</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-25,88; -18,18</t>
+          <t>-26,57; -19,53</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-66,24%</t>
+          <t>-68,28%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-62,04%</t>
+          <t>-64,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-62,76%</t>
+          <t>-65,44%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-21,73; 11,95</t>
+          <t>-23,34; 14,54</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-37,98; -4,68</t>
+          <t>-38,59; -4,67</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-81,08; -43,78</t>
+          <t>-82,23; -47,07</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4,26; 30,82</t>
+          <t>2,13; 30,81</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-34,17; -11,08</t>
+          <t>-34,29; -14,23</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-70,6; -50,74</t>
+          <t>-72,72; -54,73</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 20,97</t>
+          <t>-0,86; 20,7</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-32,21; -14,21</t>
+          <t>-31,91; -13,28</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-70,8; -53,05</t>
+          <t>-72,77; -57,28</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-10,04</t>
+          <t>-17,23</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-24,26</t>
+          <t>-23,4</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-17,27</t>
+          <t>-20,31</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,94; 6,5</t>
+          <t>1,7; 6,46</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,65; -1,14</t>
+          <t>-5,57; -1,02</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-17,54; 12,0</t>
+          <t>-19,09; -14,92</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 4,21</t>
+          <t>-0,81; 3,97</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-12,95; -8,1</t>
+          <t>-12,78; -8,11</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-27,14; -22,02</t>
+          <t>-25,41; -21,25</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,74</t>
+          <t>1,34; 4,76</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-8,71; -5,36</t>
+          <t>-8,53; -5,19</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-21,19; -4,77</t>
+          <t>-21,73; -18,93</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-35,09%</t>
+          <t>-60,22%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-65,46%</t>
+          <t>-63,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-52,55%</t>
+          <t>-61,79%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>6,46; 23,46</t>
+          <t>5,72; 23,38</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-18,96; -3,92</t>
+          <t>-18,41; -3,63</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-61,04; 43,13</t>
+          <t>-64,9; -54,5</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 11,71</t>
+          <t>-2,11; 11,14</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-33,75; -22,77</t>
+          <t>-33,25; -22,75</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-72,02; -61,21</t>
+          <t>-66,44; -59,52</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,74; 14,72</t>
+          <t>3,96; 14,69</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-25,74; -16,65</t>
+          <t>-25,38; -16,26</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-64,33; -15,1</t>
+          <t>-64,9; -59,03</t>
         </is>
       </c>
     </row>
